--- a/outputs/deliverables/requirement_3_physical_testing/test_cases/test_summary_report.xlsx
+++ b/outputs/deliverables/requirement_3_physical_testing/test_cases/test_summary_report.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="status" sheetId="1" r:id="Rb622b1e461c244b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="execution_summary" sheetId="2" r:id="R5dbcae520038408f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="3" r:id="R742fdcc157c44940"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="review" sheetId="4" r:id="Re0dc1bae69a44416"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="status" sheetId="1" r:id="Ra1617a948a9641a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="execution_summary" sheetId="2" r:id="R1554c092603e4b3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="3" r:id="R54d1b51a7f9640ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="review" sheetId="4" r:id="R171de404ca7140e4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -314,7 +314,7 @@
         <x:v>Source template</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>inputs/testcase-templates/testcase-template.xls</x:v>
+        <x:v>instructor-provided testcase-template.xls</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -376,7 +376,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf1a12f196ea451a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62cae76f2f444856"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -814,7 +814,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbd18c329d8046c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1364246f628487c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -886,7 +886,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde1a8cf6b04f4aef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5aac7854ebe4074"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -988,7 +988,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re386045bfd6e4221"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra71d8d582a124989"/>
   </x:tableParts>
 </x:worksheet>
 </file>